--- a/Lab_4/data/partB/param_optimization_process/v200_k20_s200_results.xlsx
+++ b/Lab_4/data/partB/param_optimization_process/v200_k20_s200_results.xlsx
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
         <v>2</v>
@@ -527,40 +527,40 @@
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
         <v>39</v>
       </c>
       <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L2" t="n">
         <v>2</v>
       </c>
-      <c r="K2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1</v>
-      </c>
       <c r="M2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
         <v>60</v>
@@ -579,13 +579,13 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
         <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -594,13 +594,13 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -646,13 +646,13 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -677,34 +677,34 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -738,19 +738,19 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -759,16 +759,16 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -787,19 +787,19 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G7" t="n">
+        <v>57</v>
+      </c>
+      <c r="H7" t="n">
         <v>1</v>
       </c>
-      <c r="F7" t="n">
-        <v>8</v>
-      </c>
-      <c r="G7" t="n">
-        <v>53</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -814,13 +814,13 @@
         <v>9</v>
       </c>
       <c r="N7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -842,25 +842,25 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>9</v>
@@ -869,10 +869,10 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -894,37 +894,37 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>62</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
         <v>11</v>
       </c>
-      <c r="G9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
         <v>1</v>
       </c>
-      <c r="I9" t="n">
-        <v>60</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>2</v>
-      </c>
-      <c r="P9" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -937,13 +937,13 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" t="n">
         <v>6</v>
       </c>
-      <c r="D10" t="n">
-        <v>5</v>
-      </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -958,22 +958,22 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>1</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -998,37 +998,37 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1041,16 +1041,16 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1062,13 +1062,13 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="M12" t="n">
         <v>1</v>
@@ -1077,10 +1077,10 @@
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1090,19 +1090,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
         <v>5</v>
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1123,16 +1123,16 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="N13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
         <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1142,28 +1142,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
         <v>2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
         <v>3</v>
@@ -1172,19 +1172,19 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>49</v>
+      </c>
+      <c r="O14" t="n">
         <v>1</v>
       </c>
-      <c r="M14" t="n">
-        <v>9</v>
-      </c>
-      <c r="N14" t="n">
-        <v>51</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
       <c r="P14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -1203,19 +1203,19 @@
         <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
         <v>2</v>
@@ -1224,7 +1224,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
         <v>3</v>
@@ -1246,43 +1246,43 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>2</v>
       </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
       <c r="F16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
         <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
         <v>2</v>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7982,7 +7982,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8407,7 +8407,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9087,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10175,7 +10175,7 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -10753,7 +10753,7 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -10923,7 +10923,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11127,7 +11127,7 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11739,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12300,7 +12300,7 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12334,7 +12334,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12555,7 +12555,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12657,7 +12657,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12691,7 +12691,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12827,7 +12827,7 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12929,7 +12929,7 @@
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12980,7 +12980,7 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13235,7 +13235,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13422,7 +13422,7 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13541,7 +13541,7 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13677,7 +13677,7 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14000,7 +14000,7 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14187,7 +14187,7 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14238,7 +14238,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14442,7 +14442,7 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -14578,7 +14578,7 @@
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15003,7 +15003,7 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15241,7 +15241,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -15496,7 +15496,7 @@
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15615,7 +15615,7 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -15819,7 +15819,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16380,7 +16380,7 @@
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -16397,7 +16397,7 @@
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -16890,7 +16890,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16924,7 +16924,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17077,7 +17077,7 @@
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17264,7 +17264,7 @@
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17315,7 +17315,7 @@
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17519,7 +17519,7 @@
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17536,7 +17536,7 @@
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17689,7 +17689,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17859,7 +17859,7 @@
       </c>
       <c r="C974" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17893,7 +17893,7 @@
       </c>
       <c r="C976" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -18114,7 +18114,7 @@
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18301,7 +18301,7 @@
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18369,7 +18369,7 @@
       </c>
       <c r="C1004" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18386,7 +18386,7 @@
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18420,7 +18420,7 @@
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18454,7 +18454,7 @@
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18505,7 +18505,7 @@
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18845,7 +18845,7 @@
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18896,7 +18896,7 @@
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18947,7 +18947,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18964,7 +18964,7 @@
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19083,7 +19083,7 @@
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19117,7 +19117,7 @@
       </c>
       <c r="C1048" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19202,7 +19202,7 @@
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19355,7 +19355,7 @@
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19440,7 +19440,7 @@
       </c>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19491,7 +19491,7 @@
       </c>
       <c r="C1070" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19542,7 +19542,7 @@
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="C1076" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19644,7 +19644,7 @@
       </c>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19746,7 +19746,7 @@
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19933,7 +19933,7 @@
       </c>
       <c r="C1096" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19984,7 +19984,7 @@
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="C1116" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20443,7 +20443,7 @@
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20562,7 +20562,7 @@
       </c>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -20579,7 +20579,7 @@
       </c>
       <c r="C1134" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20630,7 +20630,7 @@
       </c>
       <c r="C1137" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
       </c>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20681,7 +20681,7 @@
       </c>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20732,7 +20732,7 @@
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20953,7 +20953,7 @@
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21055,7 +21055,7 @@
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -21310,7 +21310,7 @@
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21718,7 +21718,7 @@
       </c>
       <c r="C1201" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21752,7 +21752,7 @@
       </c>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21769,7 +21769,7 @@
       </c>
       <c r="C1204" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -21786,7 +21786,7 @@
       </c>
       <c r="C1205" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -21820,7 +21820,7 @@
       </c>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -21871,7 +21871,7 @@
       </c>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21956,7 +21956,7 @@
       </c>
       <c r="C1215" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22058,7 +22058,7 @@
       </c>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -22075,7 +22075,7 @@
       </c>
       <c r="C1222" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22194,7 +22194,7 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22381,7 +22381,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22415,7 +22415,7 @@
       </c>
       <c r="C1242" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22449,7 +22449,7 @@
       </c>
       <c r="C1244" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22568,7 +22568,7 @@
       </c>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22636,7 +22636,7 @@
       </c>
       <c r="C1255" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22670,7 +22670,7 @@
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22721,7 +22721,7 @@
       </c>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -22772,7 +22772,7 @@
       </c>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -22789,7 +22789,7 @@
       </c>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -22840,7 +22840,7 @@
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22857,7 +22857,7 @@
       </c>
       <c r="C1268" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22891,7 +22891,7 @@
       </c>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22959,7 +22959,7 @@
       </c>
       <c r="C1274" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22993,7 +22993,7 @@
       </c>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23027,7 +23027,7 @@
       </c>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23044,7 +23044,7 @@
       </c>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -23197,7 +23197,7 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -23282,7 +23282,7 @@
       </c>
       <c r="C1293" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23316,7 +23316,7 @@
       </c>
       <c r="C1295" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -23350,7 +23350,7 @@
       </c>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -23469,7 +23469,7 @@
       </c>
       <c r="C1304" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23758,7 +23758,7 @@
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23877,7 +23877,7 @@
       </c>
       <c r="C1328" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -24064,7 +24064,7 @@
       </c>
       <c r="C1339" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -24370,7 +24370,7 @@
       </c>
       <c r="C1357" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="C1362" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -24557,7 +24557,7 @@
       </c>
       <c r="C1368" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -24778,7 +24778,7 @@
       </c>
       <c r="C1381" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24982,7 +24982,7 @@
       </c>
       <c r="C1393" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25016,7 +25016,7 @@
       </c>
       <c r="C1395" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="C1397" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25084,7 +25084,7 @@
       </c>
       <c r="C1399" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25118,7 +25118,7 @@
       </c>
       <c r="C1401" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -25152,7 +25152,7 @@
       </c>
       <c r="C1403" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25169,7 +25169,7 @@
       </c>
       <c r="C1404" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25509,7 +25509,7 @@
       </c>
       <c r="C1424" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -25628,7 +25628,7 @@
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25696,7 +25696,7 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -25747,7 +25747,7 @@
       </c>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25798,7 +25798,7 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -25866,7 +25866,7 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25985,7 +25985,7 @@
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -26019,7 +26019,7 @@
       </c>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26104,7 +26104,7 @@
       </c>
       <c r="C1459" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26138,7 +26138,7 @@
       </c>
       <c r="C1461" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26172,7 +26172,7 @@
       </c>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -26240,7 +26240,7 @@
       </c>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26478,7 +26478,7 @@
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="C1483" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26546,7 +26546,7 @@
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26580,7 +26580,7 @@
       </c>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="C1488" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26733,7 +26733,7 @@
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -26767,7 +26767,7 @@
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
